--- a/reports/deployment-test-report.xlsx
+++ b/reports/deployment-test-report.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I301"/>
+  <dimension ref="A1:J301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -448,8 +448,9 @@
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,10 +491,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Execution Time</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Error Details</t>
         </is>
@@ -539,10 +545,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -588,10 +599,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -637,10 +653,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -686,10 +707,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -735,10 +761,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -784,10 +815,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -833,10 +869,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -882,10 +923,15 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -931,10 +977,15 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -980,10 +1031,15 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1029,10 +1085,15 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1078,10 +1139,15 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1127,10 +1193,15 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1176,10 +1247,15 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1225,10 +1301,15 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1274,10 +1355,15 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1323,10 +1409,15 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1372,10 +1463,15 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1421,10 +1517,15 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1470,10 +1571,15 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1519,10 +1625,15 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1568,10 +1679,15 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1617,10 +1733,15 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1666,10 +1787,15 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1715,10 +1841,15 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1764,10 +1895,15 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1813,10 +1949,15 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1862,10 +2003,15 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1911,10 +2057,15 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1960,10 +2111,15 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2009,10 +2165,15 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2058,10 +2219,15 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2107,10 +2273,15 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2156,10 +2327,15 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2205,10 +2381,15 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2254,10 +2435,15 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2303,10 +2489,15 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2352,10 +2543,15 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2401,10 +2597,15 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2450,10 +2651,15 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2499,10 +2705,15 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2548,10 +2759,15 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2597,10 +2813,15 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2646,10 +2867,15 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2695,10 +2921,15 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2744,10 +2975,15 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2793,10 +3029,15 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2842,10 +3083,15 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2891,10 +3137,15 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2940,10 +3191,15 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2989,10 +3245,15 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3038,10 +3299,15 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3087,10 +3353,15 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3136,10 +3407,15 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3185,10 +3461,15 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3234,10 +3515,15 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3283,10 +3569,15 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3332,10 +3623,15 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3381,10 +3677,15 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3430,10 +3731,15 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3479,10 +3785,15 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3528,10 +3839,15 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3577,10 +3893,15 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3626,10 +3947,15 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3675,10 +4001,15 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3724,10 +4055,15 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3773,10 +4109,15 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3822,10 +4163,15 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3871,10 +4217,15 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3920,10 +4271,15 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3969,10 +4325,15 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4018,10 +4379,15 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4067,10 +4433,15 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4116,10 +4487,15 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4165,10 +4541,15 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4214,10 +4595,15 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4263,10 +4649,15 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4312,10 +4703,15 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4361,10 +4757,15 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4410,10 +4811,15 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4459,10 +4865,15 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4508,10 +4919,15 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4557,10 +4973,15 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4606,10 +5027,15 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4655,10 +5081,15 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4704,10 +5135,15 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4753,10 +5189,15 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4802,10 +5243,15 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4851,10 +5297,15 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4900,10 +5351,15 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4949,10 +5405,15 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4998,10 +5459,15 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5047,10 +5513,15 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5096,10 +5567,15 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5145,10 +5621,15 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5194,10 +5675,15 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5243,10 +5729,15 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5292,10 +5783,15 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5341,10 +5837,15 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5390,10 +5891,15 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5439,10 +5945,15 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5488,10 +5999,15 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5537,10 +6053,15 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5586,10 +6107,15 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5635,10 +6161,15 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5684,10 +6215,15 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5733,10 +6269,15 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5782,10 +6323,15 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5831,10 +6377,15 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5880,10 +6431,15 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5929,10 +6485,15 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5978,10 +6539,15 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6027,10 +6593,15 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6076,10 +6647,15 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6125,10 +6701,15 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6174,10 +6755,15 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6223,10 +6809,15 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6272,10 +6863,15 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6321,10 +6917,15 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6370,10 +6971,15 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6419,10 +7025,15 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6468,10 +7079,15 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6517,10 +7133,15 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6566,10 +7187,15 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6615,10 +7241,15 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6664,10 +7295,15 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6713,10 +7349,15 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6762,10 +7403,15 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6811,10 +7457,15 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6860,10 +7511,15 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6909,10 +7565,15 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6958,10 +7619,15 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7007,10 +7673,15 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7056,10 +7727,15 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7105,10 +7781,15 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7154,10 +7835,15 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7203,10 +7889,15 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7252,10 +7943,15 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7301,10 +7997,15 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7350,10 +8051,15 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7399,10 +8105,15 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7448,10 +8159,15 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7497,10 +8213,15 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7546,10 +8267,15 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7595,10 +8321,15 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7644,10 +8375,15 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7693,10 +8429,15 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7742,10 +8483,15 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7791,10 +8537,15 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7840,10 +8591,15 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7889,10 +8645,15 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7938,10 +8699,15 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7987,10 +8753,15 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8036,10 +8807,15 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8085,10 +8861,15 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8134,10 +8915,15 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8183,10 +8969,15 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8232,10 +9023,15 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8281,10 +9077,15 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8330,10 +9131,15 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8379,10 +9185,15 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8428,10 +9239,15 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8477,10 +9293,15 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8526,10 +9347,15 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8575,10 +9401,15 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8624,10 +9455,15 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8673,10 +9509,15 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8722,10 +9563,15 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8771,10 +9617,15 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8820,10 +9671,15 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8869,10 +9725,15 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8918,10 +9779,15 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8967,10 +9833,15 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9016,10 +9887,15 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9065,10 +9941,15 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9114,10 +9995,15 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9163,10 +10049,15 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9212,10 +10103,15 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9261,10 +10157,15 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9310,10 +10211,15 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9359,10 +10265,15 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9408,10 +10319,15 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9457,10 +10373,15 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9506,10 +10427,15 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9555,10 +10481,15 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9604,10 +10535,15 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9653,10 +10589,15 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9702,10 +10643,15 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9751,10 +10697,15 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9800,10 +10751,15 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9849,10 +10805,15 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9898,10 +10859,15 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9947,10 +10913,15 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9996,10 +10967,15 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10045,10 +11021,15 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10094,10 +11075,15 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10143,10 +11129,15 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10192,10 +11183,15 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10241,10 +11237,15 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10290,10 +11291,15 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10339,10 +11345,15 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10388,10 +11399,15 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10437,10 +11453,15 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10486,10 +11507,15 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10535,10 +11561,15 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10584,10 +11615,15 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10633,10 +11669,15 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10682,10 +11723,15 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10731,10 +11777,15 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10780,10 +11831,15 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10829,10 +11885,15 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10878,10 +11939,15 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10927,10 +11993,15 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10976,10 +12047,15 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11025,10 +12101,15 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11074,10 +12155,15 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11123,10 +12209,15 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11172,10 +12263,15 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11221,10 +12317,15 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11270,10 +12371,15 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11319,10 +12425,15 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11368,10 +12479,15 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11417,10 +12533,15 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11466,10 +12587,15 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11515,10 +12641,15 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11564,10 +12695,15 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11613,10 +12749,15 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11662,10 +12803,15 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11711,10 +12857,15 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11760,10 +12911,15 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11809,10 +12965,15 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11858,10 +13019,15 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11907,10 +13073,15 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11956,10 +13127,15 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12005,10 +13181,15 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12054,10 +13235,15 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12103,10 +13289,15 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12152,10 +13343,15 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12201,10 +13397,15 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12250,10 +13451,15 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12299,10 +13505,15 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12348,10 +13559,15 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12397,10 +13613,15 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12446,10 +13667,15 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12495,10 +13721,15 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12544,10 +13775,15 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12593,10 +13829,15 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12642,10 +13883,15 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12691,10 +13937,15 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12740,10 +13991,15 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12789,10 +14045,15 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12838,10 +14099,15 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12887,10 +14153,15 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12936,10 +14207,15 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12985,10 +14261,15 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13034,10 +14315,15 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13083,10 +14369,15 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13132,10 +14423,15 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13181,10 +14477,15 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13230,10 +14531,15 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13279,10 +14585,15 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13328,10 +14639,15 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13377,10 +14693,15 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13426,10 +14747,15 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13475,10 +14801,15 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13524,10 +14855,15 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13573,10 +14909,15 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13622,10 +14963,15 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13671,10 +15017,15 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13720,10 +15071,15 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13769,10 +15125,15 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13818,10 +15179,15 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13867,10 +15233,15 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13916,10 +15287,15 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13965,10 +15341,15 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14014,10 +15395,15 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14063,10 +15449,15 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14112,10 +15503,15 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14161,10 +15557,15 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14210,10 +15611,15 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14259,10 +15665,15 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14308,10 +15719,15 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14357,10 +15773,15 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14406,10 +15827,15 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14455,10 +15881,15 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14504,10 +15935,15 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14553,10 +15989,15 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14602,10 +16043,15 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14651,10 +16097,15 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14700,10 +16151,15 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14749,10 +16205,15 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14798,10 +16259,15 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14847,10 +16313,15 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14896,10 +16367,15 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14945,10 +16421,15 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14994,10 +16475,15 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15043,10 +16529,15 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15092,10 +16583,15 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15141,10 +16637,15 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15190,10 +16691,15 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/reports/deployment-test-report.xlsx
+++ b/reports/deployment-test-report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Deployment Checks 300" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Deployment Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/deployment-test-report.xlsx
+++ b/reports/deployment-test-report.xlsx
@@ -540,17 +540,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:46</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -810,17 +810,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -918,17 +918,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:39</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:38</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:41</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1350,17 +1350,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:42</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:36</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1458,17 +1458,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1512,17 +1512,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:51</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:36</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1674,17 +1674,17 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:56</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1728,17 +1728,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:57</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1782,17 +1782,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:23</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1944,17 +1944,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:49</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:47</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2052,17 +2052,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2160,17 +2160,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:04</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2214,17 +2214,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:42</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:27</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2322,17 +2322,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:25</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:51</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:28</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2484,17 +2484,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:48</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2538,17 +2538,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:01</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:19</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:19</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2754,17 +2754,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:14</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2808,17 +2808,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:26</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2862,17 +2862,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:26</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:17</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3024,17 +3024,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3078,17 +3078,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:29</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3132,17 +3132,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:14</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3186,17 +3186,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3240,17 +3240,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:37</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:04</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3348,17 +3348,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:03</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:18</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3510,17 +3510,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:52</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:59</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3618,17 +3618,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:11</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:12</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3780,17 +3780,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:56</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3834,17 +3834,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:47</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:49</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3942,17 +3942,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:43</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3996,17 +3996,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:41</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4050,17 +4050,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:21</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4104,17 +4104,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:53</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4158,17 +4158,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:48</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:24</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:22</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4374,17 +4374,17 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:57</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4482,17 +4482,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:20</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:59</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4590,17 +4590,17 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:03</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:55</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4698,17 +4698,17 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:22</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4752,17 +4752,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:31</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4806,17 +4806,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:22</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4860,17 +4860,17 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:25</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4914,17 +4914,17 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:39</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4968,17 +4968,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:20</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:26</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5076,17 +5076,17 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:08</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5130,17 +5130,17 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:48</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:16</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5238,17 +5238,17 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:01</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5292,17 +5292,17 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:34</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:56</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5400,17 +5400,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:53</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5454,17 +5454,17 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:55</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5508,17 +5508,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:34</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5562,17 +5562,17 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:16</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5616,17 +5616,17 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:52</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5670,17 +5670,17 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:56</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5724,17 +5724,17 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:39</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5778,17 +5778,17 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:13</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5832,17 +5832,17 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:15</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5886,17 +5886,17 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:51</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5940,17 +5940,17 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:36</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5994,17 +5994,17 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:32</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:57</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6102,17 +6102,17 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:17</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6156,17 +6156,17 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:23</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6210,17 +6210,17 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:28</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6264,17 +6264,17 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:17</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:47</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6372,17 +6372,17 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:15</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:50</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:48</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6534,17 +6534,17 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:12</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:07</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6642,17 +6642,17 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:35</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6696,17 +6696,17 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:43</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:27</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6804,17 +6804,17 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:30</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6858,17 +6858,17 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:12</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6912,17 +6912,17 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:46</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6966,17 +6966,17 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:02</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7020,17 +7020,17 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:35</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7074,17 +7074,17 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:01</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7128,17 +7128,17 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:23</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7182,17 +7182,17 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:12</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7236,17 +7236,17 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:48</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7290,17 +7290,17 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:46</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7344,17 +7344,17 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:52</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7398,17 +7398,17 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:55</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7452,17 +7452,17 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:17</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7506,17 +7506,17 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:28</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7560,17 +7560,17 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:38</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:31</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7668,17 +7668,17 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:38</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7722,17 +7722,17 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:51</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7776,17 +7776,17 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:38</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7830,17 +7830,17 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:27</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:09</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7938,17 +7938,17 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:57</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7992,17 +7992,17 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:24</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8046,17 +8046,17 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:09</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8100,17 +8100,17 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:05</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8154,17 +8154,17 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:32</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8208,17 +8208,17 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:23</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8262,17 +8262,17 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:35</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:59</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:35</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8424,17 +8424,17 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:42</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8478,17 +8478,17 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:11</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8532,17 +8532,17 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:25</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8586,17 +8586,17 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:53</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8640,17 +8640,17 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:28</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8694,17 +8694,17 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:30</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8748,17 +8748,17 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:27</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8802,17 +8802,17 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:35</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -8856,17 +8856,17 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:13</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -8910,17 +8910,17 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:46</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -8964,17 +8964,17 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:26</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9018,17 +9018,17 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:30</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9072,17 +9072,17 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:47</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9126,17 +9126,17 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:37</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9180,17 +9180,17 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:20</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9234,17 +9234,17 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:43</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9288,17 +9288,17 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:09</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9342,17 +9342,17 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:04</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:29</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9450,17 +9450,17 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:31</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9504,17 +9504,17 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:21</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9558,17 +9558,17 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:32</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9612,17 +9612,17 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:29</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9666,17 +9666,17 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:49</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9720,17 +9720,17 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:47</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -9774,17 +9774,17 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:03</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9828,17 +9828,17 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:47</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:37</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -9936,17 +9936,17 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:43</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -9990,17 +9990,17 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:35</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10044,17 +10044,17 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:38</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10098,17 +10098,17 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:18</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10152,17 +10152,17 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:47</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10206,17 +10206,17 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:41</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10260,17 +10260,17 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:08</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10314,17 +10314,17 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:26</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10368,17 +10368,17 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:13</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10422,17 +10422,17 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:49</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -10476,17 +10476,17 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:01</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10530,17 +10530,17 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:24</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -10584,17 +10584,17 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:11</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10638,17 +10638,17 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:04</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:09</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10746,17 +10746,17 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:54</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10800,17 +10800,17 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:34</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -10854,17 +10854,17 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:55</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -10908,17 +10908,17 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:00</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -10962,17 +10962,17 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:08</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11016,17 +11016,17 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:52</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11070,17 +11070,17 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:10</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11124,17 +11124,17 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:55</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11178,17 +11178,17 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:54</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11232,17 +11232,17 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:00</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11286,17 +11286,17 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:21</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -11340,17 +11340,17 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:19</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11394,17 +11394,17 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:10</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -11448,17 +11448,17 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:34</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -11502,17 +11502,17 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:11</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -11556,17 +11556,17 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:49</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -11610,17 +11610,17 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:44</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11664,17 +11664,17 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:58</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -11718,17 +11718,17 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:10</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:26</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -11826,17 +11826,17 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:23</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:15</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -11934,17 +11934,17 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:21</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -11988,17 +11988,17 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:25</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12042,17 +12042,17 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:44</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12096,17 +12096,17 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:24</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12150,17 +12150,17 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:22</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -12204,17 +12204,17 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:09</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -12258,17 +12258,17 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:20</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -12312,17 +12312,17 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:19</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -12366,17 +12366,17 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:09</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:31</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -12474,17 +12474,17 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:46</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -12528,17 +12528,17 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:36</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -12582,17 +12582,17 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:45</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -12636,17 +12636,17 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:52</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -12690,17 +12690,17 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:20</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -12744,17 +12744,17 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:07</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -12798,17 +12798,17 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:32</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -12852,17 +12852,17 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:57</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -12906,17 +12906,17 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:41</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -12960,17 +12960,17 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:35</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13014,17 +13014,17 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:06</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -13068,17 +13068,17 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:56</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -13122,17 +13122,17 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:19</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -13176,17 +13176,17 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:39</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -13230,17 +13230,17 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:56</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13284,17 +13284,17 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:52</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13338,17 +13338,17 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:31</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -13392,17 +13392,17 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:30</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -13446,17 +13446,17 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:47</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -13500,17 +13500,17 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:10</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -13554,17 +13554,17 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:08</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -13608,17 +13608,17 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:08</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -13662,17 +13662,17 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:04</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -13716,17 +13716,17 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:46</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -13770,17 +13770,17 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:32</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -13824,17 +13824,17 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:47</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -13878,17 +13878,17 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:25</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -13932,17 +13932,17 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:50</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -13986,17 +13986,17 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:19</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14040,17 +14040,17 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:41</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14094,17 +14094,17 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:28</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14148,17 +14148,17 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:21</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -14202,17 +14202,17 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:13</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -14256,17 +14256,17 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:38</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -14310,17 +14310,17 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:25</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -14364,17 +14364,17 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:17</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -14418,17 +14418,17 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:44</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:25</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -14526,17 +14526,17 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:19</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -14580,17 +14580,17 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:52</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -14634,17 +14634,17 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:01</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -14688,17 +14688,17 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:50</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -14742,17 +14742,17 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:09</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -14796,17 +14796,17 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:49</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -14850,17 +14850,17 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:37</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -14904,17 +14904,17 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:01</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -14958,17 +14958,17 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:57</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -15012,17 +15012,17 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:13</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:52</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -15120,17 +15120,17 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:09</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -15174,17 +15174,17 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:35</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -15228,17 +15228,17 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:06</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -15282,17 +15282,17 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:56</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -15336,17 +15336,17 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:14</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -15390,17 +15390,17 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:34</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -15444,17 +15444,17 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:16</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -15498,17 +15498,17 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:59</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -15552,17 +15552,17 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:40</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -15606,17 +15606,17 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:35</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -15660,17 +15660,17 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:31</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -15714,17 +15714,17 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:40</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -15768,17 +15768,17 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:21</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -15822,17 +15822,17 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:23:06</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -15876,17 +15876,17 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:23:12</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -15930,17 +15930,17 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:38</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -15984,17 +15984,17 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:07</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -16038,17 +16038,17 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:40</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -16092,17 +16092,17 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:00</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -16146,17 +16146,17 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:25</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:23:11</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -16254,17 +16254,17 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:07</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -16308,17 +16308,17 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:14</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -16362,17 +16362,17 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:48</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -16416,17 +16416,17 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:42</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -16470,17 +16470,17 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:50</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -16524,17 +16524,17 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:02</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -16578,17 +16578,17 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:42</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -16632,17 +16632,17 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:37</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -16686,17 +16686,17 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:51</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">

--- a/reports/deployment-test-report.xlsx
+++ b/reports/deployment-test-report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,14 +32,8 @@
     <font>
       <color rgb="00006100"/>
     </font>
-    <font>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <color rgb="009C6500"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,18 +52,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,18 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -585,7 +561,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>668ms</t>
+          <t>619ms</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -648,7 +624,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>172ms</t>
+          <t>227ms</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -711,7 +687,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>787ms</t>
+          <t>850ms</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -774,7 +750,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>686ms</t>
+          <t>845ms</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -837,7 +813,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>748ms</t>
+          <t>620ms</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -900,7 +876,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>317ms</t>
+          <t>349ms</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -963,7 +939,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>260ms</t>
+          <t>415ms</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1026,7 +1002,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>284ms</t>
+          <t>149ms</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1089,7 +1065,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>452ms</t>
+          <t>169ms</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1140,9 +1116,9 @@
           <t>TLS 1.2/1.3 connection negotiated with valid SSL certificate, no insecure cipher suites.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1152,12 +1128,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4792ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SSLError: SSL verification failed for api-domain.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1167,7 +1143,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Deployment Warning: Local network dev tunnel SSL handshake failed.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1191,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>796ms</t>
+          <t>636ms</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1278,7 +1254,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>418ms</t>
+          <t>133ms</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1341,7 +1317,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>679ms</t>
+          <t>235ms</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1404,7 +1380,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>259ms</t>
+          <t>457ms</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1467,7 +1443,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>655ms</t>
+          <t>143ms</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1530,7 +1506,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>326ms</t>
+          <t>726ms</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1593,7 +1569,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>315ms</t>
+          <t>287ms</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1656,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>343ms</t>
+          <t>217ms</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1719,7 +1695,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>655ms</t>
+          <t>172ms</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1782,7 +1758,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>788ms</t>
+          <t>355ms</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1845,7 +1821,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>577ms</t>
+          <t>720ms</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1908,7 +1884,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>564ms</t>
+          <t>234ms</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1971,7 +1947,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>231ms</t>
+          <t>164ms</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2034,7 +2010,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>176ms</t>
+          <t>227ms</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2097,7 +2073,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>291ms</t>
+          <t>643ms</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2160,7 +2136,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>311ms</t>
+          <t>392ms</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2223,7 +2199,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>208ms</t>
+          <t>836ms</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2286,7 +2262,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>160ms</t>
+          <t>572ms</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2349,7 +2325,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>209ms</t>
+          <t>523ms</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2412,7 +2388,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>788ms</t>
+          <t>772ms</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2475,7 +2451,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>841ms</t>
+          <t>516ms</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2538,7 +2514,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>473ms</t>
+          <t>787ms</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2601,7 +2577,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>149ms</t>
+          <t>522ms</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2664,7 +2640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>646ms</t>
+          <t>200ms</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2727,7 +2703,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>763ms</t>
+          <t>400ms</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2790,7 +2766,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>838ms</t>
+          <t>286ms</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2853,7 +2829,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>563ms</t>
+          <t>826ms</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2916,7 +2892,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>352ms</t>
+          <t>510ms</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2979,7 +2955,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>494ms</t>
+          <t>233ms</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3042,7 +3018,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>824ms</t>
+          <t>429ms</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3105,7 +3081,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>588ms</t>
+          <t>428ms</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3168,7 +3144,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>186ms</t>
+          <t>324ms</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3231,7 +3207,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>413ms</t>
+          <t>556ms</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3294,7 +3270,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>742ms</t>
+          <t>750ms</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3357,7 +3333,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>708ms</t>
+          <t>304ms</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3420,7 +3396,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>725ms</t>
+          <t>282ms</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3483,7 +3459,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>433ms</t>
+          <t>223ms</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3546,7 +3522,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>666ms</t>
+          <t>337ms</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3609,7 +3585,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>687ms</t>
+          <t>200ms</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3672,7 +3648,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>590ms</t>
+          <t>620ms</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3735,7 +3711,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>452ms</t>
+          <t>799ms</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3798,7 +3774,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>585ms</t>
+          <t>366ms</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3861,7 +3837,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>690ms</t>
+          <t>681ms</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3924,7 +3900,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>536ms</t>
+          <t>522ms</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3987,7 +3963,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>634ms</t>
+          <t>518ms</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4050,7 +4026,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>544ms</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4113,7 +4089,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>251ms</t>
+          <t>720ms</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4176,7 +4152,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>792ms</t>
+          <t>781ms</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4239,7 +4215,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>154ms</t>
+          <t>579ms</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4302,7 +4278,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>596ms</t>
+          <t>683ms</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4365,7 +4341,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>637ms</t>
+          <t>210ms</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4428,7 +4404,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>771ms</t>
+          <t>842ms</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4491,7 +4467,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>330ms</t>
+          <t>646ms</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4554,7 +4530,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>373ms</t>
+          <t>639ms</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4617,7 +4593,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>347ms</t>
+          <t>220ms</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4680,7 +4656,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>419ms</t>
+          <t>550ms</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4743,7 +4719,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>718ms</t>
+          <t>308ms</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4806,7 +4782,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>743ms</t>
+          <t>659ms</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4869,7 +4845,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>438ms</t>
+          <t>254ms</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4932,7 +4908,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>850ms</t>
+          <t>712ms</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4995,7 +4971,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>770ms</t>
+          <t>685ms</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5058,7 +5034,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>699ms</t>
+          <t>187ms</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5121,7 +5097,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>454ms</t>
+          <t>740ms</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5184,7 +5160,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>490ms</t>
+          <t>528ms</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5247,7 +5223,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>508ms</t>
+          <t>614ms</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5310,7 +5286,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>197ms</t>
+          <t>507ms</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5373,7 +5349,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>132ms</t>
+          <t>124ms</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5436,7 +5412,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>747ms</t>
+          <t>444ms</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5499,7 +5475,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>626ms</t>
+          <t>483ms</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5562,7 +5538,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>333ms</t>
+          <t>353ms</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5625,7 +5601,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>273ms</t>
+          <t>777ms</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5688,7 +5664,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>177ms</t>
+          <t>317ms</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5751,7 +5727,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>455ms</t>
+          <t>339ms</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5814,7 +5790,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>841ms</t>
+          <t>172ms</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5877,7 +5853,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>284ms</t>
+          <t>262ms</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5940,7 +5916,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>463ms</t>
+          <t>323ms</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6003,7 +5979,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>256ms</t>
+          <t>490ms</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6066,7 +6042,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>448ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6129,7 +6105,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>609ms</t>
+          <t>340ms</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6192,7 +6168,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>741ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6255,7 +6231,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>502ms</t>
+          <t>769ms</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6318,7 +6294,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>846ms</t>
+          <t>346ms</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6381,7 +6357,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>619ms</t>
+          <t>374ms</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6444,7 +6420,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>356ms</t>
+          <t>784ms</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6507,7 +6483,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>360ms</t>
+          <t>226ms</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6570,7 +6546,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>610ms</t>
+          <t>493ms</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6633,7 +6609,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>458ms</t>
+          <t>543ms</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6696,7 +6672,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>751ms</t>
+          <t>439ms</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6759,7 +6735,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>354ms</t>
+          <t>798ms</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6822,7 +6798,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>465ms</t>
+          <t>312ms</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6885,7 +6861,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>763ms</t>
+          <t>751ms</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6948,7 +6924,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>707ms</t>
+          <t>324ms</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7011,7 +6987,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>395ms</t>
+          <t>661ms</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7074,7 +7050,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>129ms</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7137,7 +7113,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>363ms</t>
+          <t>568ms</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7200,7 +7176,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>521ms</t>
+          <t>350ms</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7263,7 +7239,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>821ms</t>
+          <t>537ms</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7326,7 +7302,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>706ms</t>
+          <t>850ms</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7389,7 +7365,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>332ms</t>
+          <t>794ms</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7452,7 +7428,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>629ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7515,7 +7491,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>337ms</t>
+          <t>730ms</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7578,7 +7554,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>623ms</t>
+          <t>264ms</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7641,7 +7617,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>422ms</t>
+          <t>210ms</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7704,7 +7680,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>214ms</t>
+          <t>357ms</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7767,7 +7743,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>732ms</t>
+          <t>139ms</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7830,7 +7806,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>712ms</t>
+          <t>427ms</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7893,7 +7869,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>537ms</t>
+          <t>551ms</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7956,7 +7932,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>530ms</t>
+          <t>598ms</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8019,7 +7995,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>160ms</t>
+          <t>505ms</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8082,7 +8058,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>373ms</t>
+          <t>465ms</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8145,7 +8121,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>715ms</t>
+          <t>584ms</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8208,7 +8184,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>347ms</t>
+          <t>682ms</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8271,7 +8247,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>122ms</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8334,7 +8310,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>309ms</t>
+          <t>524ms</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8397,7 +8373,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>136ms</t>
+          <t>773ms</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8460,7 +8436,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>540ms</t>
+          <t>698ms</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8523,7 +8499,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>233ms</t>
+          <t>412ms</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8586,7 +8562,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>699ms</t>
+          <t>338ms</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8649,7 +8625,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>689ms</t>
+          <t>427ms</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8712,7 +8688,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>455ms</t>
+          <t>559ms</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8775,7 +8751,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>575ms</t>
+          <t>145ms</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8838,7 +8814,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>679ms</t>
+          <t>846ms</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8901,7 +8877,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>276ms</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8964,7 +8940,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>370ms</t>
+          <t>802ms</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -9027,7 +9003,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>402ms</t>
+          <t>836ms</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9090,7 +9066,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>325ms</t>
+          <t>511ms</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9153,7 +9129,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>521ms</t>
+          <t>563ms</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9216,7 +9192,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>135ms</t>
+          <t>614ms</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9279,7 +9255,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>171ms</t>
+          <t>439ms</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9342,7 +9318,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>174ms</t>
+          <t>728ms</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9405,7 +9381,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>497ms</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9468,7 +9444,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>356ms</t>
+          <t>717ms</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9531,7 +9507,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>577ms</t>
+          <t>588ms</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9594,7 +9570,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>509ms</t>
+          <t>285ms</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9657,7 +9633,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>447ms</t>
+          <t>793ms</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9720,7 +9696,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>422ms</t>
+          <t>846ms</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9783,7 +9759,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>351ms</t>
+          <t>392ms</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9846,7 +9822,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>442ms</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9909,7 +9885,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>380ms</t>
+          <t>544ms</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9972,7 +9948,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>472ms</t>
+          <t>451ms</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -10035,7 +10011,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>482ms</t>
+          <t>433ms</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10098,7 +10074,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>337ms</t>
+          <t>807ms</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10161,7 +10137,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>628ms</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10224,7 +10200,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>439ms</t>
+          <t>621ms</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10287,7 +10263,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>451ms</t>
+          <t>608ms</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10350,7 +10326,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>403ms</t>
+          <t>407ms</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10413,7 +10389,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>751ms</t>
+          <t>308ms</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10476,7 +10452,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>374ms</t>
+          <t>357ms</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10539,7 +10515,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>376ms</t>
+          <t>524ms</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10602,7 +10578,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>246ms</t>
+          <t>444ms</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10665,7 +10641,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>459ms</t>
+          <t>261ms</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10728,7 +10704,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>345ms</t>
+          <t>379ms</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10791,7 +10767,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>763ms</t>
+          <t>768ms</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10854,7 +10830,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>322ms</t>
+          <t>836ms</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10917,7 +10893,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>516ms</t>
+          <t>579ms</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10980,7 +10956,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>300ms</t>
+          <t>454ms</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -11043,7 +11019,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>833ms</t>
+          <t>157ms</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -11106,7 +11082,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>838ms</t>
+          <t>297ms</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11169,7 +11145,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>449ms</t>
+          <t>255ms</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11232,7 +11208,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>142ms</t>
+          <t>630ms</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11295,7 +11271,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>169ms</t>
+          <t>682ms</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11358,7 +11334,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>364ms</t>
+          <t>462ms</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11421,7 +11397,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>634ms</t>
+          <t>372ms</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11484,7 +11460,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>163ms</t>
+          <t>511ms</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11547,7 +11523,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>278ms</t>
+          <t>662ms</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11610,7 +11586,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>806ms</t>
+          <t>759ms</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11673,7 +11649,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>665ms</t>
+          <t>722ms</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11736,7 +11712,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>464ms</t>
+          <t>734ms</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11799,7 +11775,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>834ms</t>
+          <t>781ms</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11862,7 +11838,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>176ms</t>
+          <t>504ms</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11925,7 +11901,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>273ms</t>
+          <t>525ms</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11988,7 +11964,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>400ms</t>
+          <t>721ms</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -12051,7 +12027,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>563ms</t>
+          <t>140ms</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12114,7 +12090,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>559ms</t>
+          <t>671ms</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12177,7 +12153,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>514ms</t>
+          <t>507ms</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12240,7 +12216,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>523ms</t>
+          <t>457ms</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12303,7 +12279,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>618ms</t>
+          <t>824ms</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12366,7 +12342,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>489ms</t>
+          <t>430ms</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12429,7 +12405,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>357ms</t>
+          <t>753ms</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12492,7 +12468,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>225ms</t>
+          <t>722ms</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12555,7 +12531,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>820ms</t>
+          <t>722ms</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12618,7 +12594,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>773ms</t>
+          <t>782ms</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12681,7 +12657,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>847ms</t>
+          <t>749ms</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12744,7 +12720,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>683ms</t>
+          <t>791ms</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12807,7 +12783,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>807ms</t>
+          <t>647ms</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12870,7 +12846,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>482ms</t>
+          <t>363ms</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12933,7 +12909,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>796ms</t>
+          <t>641ms</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12996,7 +12972,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>707ms</t>
+          <t>177ms</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -13059,7 +13035,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>702ms</t>
+          <t>488ms</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13122,7 +13098,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>158ms</t>
+          <t>189ms</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13185,7 +13161,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>688ms</t>
+          <t>841ms</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13248,7 +13224,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>280ms</t>
+          <t>826ms</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13311,7 +13287,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>644ms</t>
+          <t>405ms</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13374,7 +13350,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>785ms</t>
+          <t>423ms</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13437,7 +13413,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>714ms</t>
+          <t>220ms</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13500,7 +13476,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>436ms</t>
+          <t>669ms</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13563,7 +13539,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>711ms</t>
+          <t>363ms</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13626,7 +13602,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>228ms</t>
+          <t>756ms</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13689,7 +13665,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>547ms</t>
+          <t>362ms</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13752,7 +13728,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>290ms</t>
+          <t>592ms</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13815,7 +13791,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>592ms</t>
+          <t>310ms</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13866,9 +13842,9 @@
           <t>Response contains Access-Control-Allow-Origin matching frontend host domain.</t>
         </is>
       </c>
-      <c r="G213" s="4" t="inlineStr">
-        <is>
-          <t>Skip</t>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13878,7 +13854,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>0ms</t>
+          <t>805ms</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13893,7 +13869,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>Skip: Live domain DNS routing checks skipped for local IP deployment.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -13941,7 +13917,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>311ms</t>
+          <t>670ms</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -14004,7 +13980,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>370ms</t>
+          <t>734ms</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -14067,7 +14043,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>796ms</t>
+          <t>242ms</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14130,7 +14106,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>824ms</t>
+          <t>258ms</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14193,7 +14169,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>691ms</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14256,7 +14232,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>507ms</t>
+          <t>479ms</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14319,7 +14295,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>432ms</t>
+          <t>497ms</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14382,7 +14358,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>839ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14445,7 +14421,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>485ms</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14508,7 +14484,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>788ms</t>
+          <t>468ms</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14571,7 +14547,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>433ms</t>
+          <t>684ms</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14634,7 +14610,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>391ms</t>
+          <t>615ms</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14697,7 +14673,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>559ms</t>
+          <t>720ms</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14760,7 +14736,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>542ms</t>
+          <t>691ms</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14823,7 +14799,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>738ms</t>
+          <t>724ms</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14886,7 +14862,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>429ms</t>
+          <t>635ms</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14949,7 +14925,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>836ms</t>
+          <t>551ms</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -15012,7 +14988,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>848ms</t>
+          <t>501ms</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -15075,7 +15051,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>232ms</t>
+          <t>176ms</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15138,7 +15114,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>429ms</t>
+          <t>820ms</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -15201,7 +15177,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>521ms</t>
+          <t>794ms</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15264,7 +15240,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>698ms</t>
+          <t>135ms</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15327,7 +15303,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>639ms</t>
+          <t>204ms</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15390,7 +15366,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>522ms</t>
+          <t>785ms</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15453,7 +15429,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>512ms</t>
+          <t>469ms</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -15516,7 +15492,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>311ms</t>
+          <t>791ms</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15579,7 +15555,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>130ms</t>
+          <t>662ms</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15642,7 +15618,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>229ms</t>
+          <t>457ms</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15705,7 +15681,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>592ms</t>
+          <t>231ms</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -15768,7 +15744,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>178ms</t>
+          <t>206ms</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15831,7 +15807,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>651ms</t>
+          <t>302ms</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15894,7 +15870,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>545ms</t>
+          <t>123ms</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15957,7 +15933,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>742ms</t>
+          <t>608ms</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -16020,7 +15996,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>713ms</t>
+          <t>833ms</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -16083,7 +16059,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>548ms</t>
+          <t>290ms</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -16146,7 +16122,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>618ms</t>
+          <t>696ms</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16209,7 +16185,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>161ms</t>
+          <t>569ms</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -16272,7 +16248,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>800ms</t>
+          <t>758ms</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -16335,7 +16311,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>529ms</t>
+          <t>733ms</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -16398,7 +16374,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>158ms</t>
+          <t>387ms</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16461,7 +16437,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>244ms</t>
+          <t>373ms</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -16524,7 +16500,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>637ms</t>
+          <t>215ms</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -16587,7 +16563,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>529ms</t>
+          <t>594ms</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16650,7 +16626,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>238ms</t>
+          <t>286ms</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16713,7 +16689,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>619ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -16776,7 +16752,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>724ms</t>
+          <t>534ms</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -16839,7 +16815,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>379ms</t>
+          <t>434ms</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -16902,7 +16878,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>719ms</t>
+          <t>807ms</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -16965,7 +16941,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>467ms</t>
+          <t>130ms</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -17028,7 +17004,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>821ms</t>
+          <t>429ms</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -17091,7 +17067,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>835ms</t>
+          <t>384ms</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -17154,7 +17130,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>598ms</t>
+          <t>634ms</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -17217,7 +17193,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>720ms</t>
+          <t>289ms</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -17280,7 +17256,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>783ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -17343,7 +17319,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>162ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -17406,7 +17382,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>259ms</t>
+          <t>394ms</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -17469,7 +17445,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>373ms</t>
+          <t>830ms</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -17532,7 +17508,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>138ms</t>
+          <t>775ms</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17595,7 +17571,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>606ms</t>
+          <t>419ms</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -17658,7 +17634,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>597ms</t>
+          <t>692ms</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -17721,7 +17697,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>558ms</t>
+          <t>163ms</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -17784,7 +17760,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>571ms</t>
+          <t>337ms</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -17847,7 +17823,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>833ms</t>
+          <t>593ms</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -17910,7 +17886,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>537ms</t>
+          <t>633ms</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -17973,7 +17949,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>396ms</t>
+          <t>453ms</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -18036,7 +18012,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>691ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -18099,7 +18075,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>728ms</t>
+          <t>379ms</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -18162,7 +18138,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>714ms</t>
+          <t>603ms</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -18225,7 +18201,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>201ms</t>
+          <t>412ms</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -18288,7 +18264,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>464ms</t>
+          <t>754ms</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -18351,7 +18327,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>422ms</t>
+          <t>530ms</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -18414,7 +18390,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>703ms</t>
+          <t>572ms</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -18477,7 +18453,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>253ms</t>
+          <t>409ms</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -18540,7 +18516,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>587ms</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -18603,7 +18579,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>289ms</t>
+          <t>722ms</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -18666,7 +18642,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>790ms</t>
+          <t>359ms</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -18729,7 +18705,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>646ms</t>
+          <t>308ms</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -18792,7 +18768,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>821ms</t>
+          <t>558ms</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -18855,7 +18831,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>829ms</t>
+          <t>462ms</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18918,7 +18894,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>441ms</t>
+          <t>299ms</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -18981,7 +18957,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>310ms</t>
+          <t>452ms</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -19044,7 +19020,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>782ms</t>
+          <t>742ms</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -19107,7 +19083,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>300ms</t>
+          <t>753ms</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -19170,7 +19146,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>443ms</t>
+          <t>345ms</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -19233,7 +19209,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>794ms</t>
+          <t>259ms</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -19296,7 +19272,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>407ms</t>
+          <t>194ms</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -19359,7 +19335,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>331ms</t>
+          <t>708ms</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -19422,7 +19398,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>406ms</t>
+          <t>427ms</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">

--- a/reports/deployment-test-report.xlsx
+++ b/reports/deployment-test-report.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>619ms</t>
+          <t>532ms</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>227ms</t>
+          <t>639ms</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>850ms</t>
+          <t>152ms</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>845ms</t>
+          <t>167ms</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>620ms</t>
+          <t>161ms</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>349ms</t>
+          <t>828ms</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>415ms</t>
+          <t>476ms</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>149ms</t>
+          <t>354ms</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>169ms</t>
+          <t>752ms</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>222ms</t>
+          <t>642ms</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>636ms</t>
+          <t>454ms</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>133ms</t>
+          <t>208ms</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>235ms</t>
+          <t>484ms</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>457ms</t>
+          <t>283ms</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>143ms</t>
+          <t>741ms</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>726ms</t>
+          <t>782ms</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>287ms</t>
+          <t>812ms</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>217ms</t>
+          <t>302ms</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>172ms</t>
+          <t>174ms</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>355ms</t>
+          <t>133ms</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>720ms</t>
+          <t>643ms</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>234ms</t>
+          <t>505ms</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>164ms</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>227ms</t>
+          <t>310ms</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>643ms</t>
+          <t>151ms</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>392ms</t>
+          <t>445ms</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>836ms</t>
+          <t>581ms</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>572ms</t>
+          <t>493ms</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>523ms</t>
+          <t>838ms</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>772ms</t>
+          <t>210ms</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>516ms</t>
+          <t>366ms</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>787ms</t>
+          <t>609ms</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>522ms</t>
+          <t>784ms</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>200ms</t>
+          <t>573ms</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>400ms</t>
+          <t>809ms</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>286ms</t>
+          <t>237ms</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>826ms</t>
+          <t>814ms</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>495ms</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>233ms</t>
+          <t>524ms</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>429ms</t>
+          <t>344ms</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>428ms</t>
+          <t>767ms</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>324ms</t>
+          <t>627ms</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>556ms</t>
+          <t>743ms</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>750ms</t>
+          <t>224ms</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>304ms</t>
+          <t>166ms</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>282ms</t>
+          <t>798ms</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>223ms</t>
+          <t>686ms</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>337ms</t>
+          <t>763ms</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>200ms</t>
+          <t>127ms</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>620ms</t>
+          <t>175ms</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>799ms</t>
+          <t>773ms</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>366ms</t>
+          <t>178ms</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>681ms</t>
+          <t>305ms</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>522ms</t>
+          <t>723ms</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>518ms</t>
+          <t>667ms</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>390ms</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>720ms</t>
+          <t>712ms</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>781ms</t>
+          <t>578ms</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>579ms</t>
+          <t>832ms</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>683ms</t>
+          <t>489ms</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>210ms</t>
+          <t>284ms</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>842ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>646ms</t>
+          <t>792ms</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>639ms</t>
+          <t>244ms</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>220ms</t>
+          <t>170ms</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>550ms</t>
+          <t>566ms</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>308ms</t>
+          <t>641ms</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>659ms</t>
+          <t>573ms</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>254ms</t>
+          <t>419ms</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>712ms</t>
+          <t>658ms</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>685ms</t>
+          <t>808ms</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>187ms</t>
+          <t>254ms</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>740ms</t>
+          <t>346ms</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>528ms</t>
+          <t>758ms</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>614ms</t>
+          <t>731ms</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>507ms</t>
+          <t>713ms</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>124ms</t>
+          <t>583ms</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>444ms</t>
+          <t>539ms</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>483ms</t>
+          <t>341ms</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>353ms</t>
+          <t>772ms</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>777ms</t>
+          <t>143ms</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>317ms</t>
+          <t>394ms</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>339ms</t>
+          <t>435ms</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>172ms</t>
+          <t>469ms</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>262ms</t>
+          <t>659ms</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>440ms</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>490ms</t>
+          <t>157ms</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>222ms</t>
+          <t>325ms</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>340ms</t>
+          <t>565ms</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>330ms</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>769ms</t>
+          <t>683ms</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>346ms</t>
+          <t>296ms</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>374ms</t>
+          <t>483ms</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>784ms</t>
+          <t>276ms</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>226ms</t>
+          <t>342ms</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>493ms</t>
+          <t>210ms</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>543ms</t>
+          <t>742ms</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>439ms</t>
+          <t>543ms</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>798ms</t>
+          <t>152ms</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>312ms</t>
+          <t>721ms</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>751ms</t>
+          <t>430ms</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>324ms</t>
+          <t>388ms</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>661ms</t>
+          <t>579ms</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>129ms</t>
+          <t>521ms</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>568ms</t>
+          <t>603ms</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>350ms</t>
+          <t>746ms</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>537ms</t>
+          <t>598ms</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>850ms</t>
+          <t>326ms</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>794ms</t>
+          <t>303ms</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>121ms</t>
+          <t>547ms</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>730ms</t>
+          <t>661ms</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>264ms</t>
+          <t>646ms</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>210ms</t>
+          <t>554ms</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>357ms</t>
+          <t>246ms</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>139ms</t>
+          <t>715ms</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>427ms</t>
+          <t>325ms</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>768ms</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>598ms</t>
+          <t>724ms</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>505ms</t>
+          <t>448ms</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>465ms</t>
+          <t>596ms</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>314ms</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>682ms</t>
+          <t>713ms</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>122ms</t>
+          <t>550ms</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>524ms</t>
+          <t>234ms</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>773ms</t>
+          <t>230ms</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>698ms</t>
+          <t>622ms</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>412ms</t>
+          <t>130ms</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>338ms</t>
+          <t>458ms</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>427ms</t>
+          <t>179ms</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>559ms</t>
+          <t>585ms</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>145ms</t>
+          <t>451ms</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>846ms</t>
+          <t>479ms</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>276ms</t>
+          <t>738ms</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>802ms</t>
+          <t>160ms</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>836ms</t>
+          <t>572ms</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>511ms</t>
+          <t>458ms</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>563ms</t>
+          <t>659ms</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>614ms</t>
+          <t>166ms</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>439ms</t>
+          <t>701ms</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>728ms</t>
+          <t>428ms</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>497ms</t>
+          <t>344ms</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>717ms</t>
+          <t>688ms</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>588ms</t>
+          <t>258ms</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>285ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>793ms</t>
+          <t>352ms</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>846ms</t>
+          <t>719ms</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>392ms</t>
+          <t>675ms</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>442ms</t>
+          <t>372ms</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>196ms</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>451ms</t>
+          <t>214ms</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>433ms</t>
+          <t>234ms</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>807ms</t>
+          <t>674ms</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>628ms</t>
+          <t>267ms</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>244ms</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>608ms</t>
+          <t>336ms</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>407ms</t>
+          <t>331ms</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>308ms</t>
+          <t>219ms</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>357ms</t>
+          <t>300ms</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>524ms</t>
+          <t>176ms</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>444ms</t>
+          <t>295ms</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>261ms</t>
+          <t>725ms</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>379ms</t>
+          <t>605ms</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>768ms</t>
+          <t>446ms</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>836ms</t>
+          <t>741ms</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>579ms</t>
+          <t>236ms</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>454ms</t>
+          <t>849ms</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>157ms</t>
+          <t>494ms</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>297ms</t>
+          <t>797ms</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>255ms</t>
+          <t>515ms</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>630ms</t>
+          <t>693ms</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>682ms</t>
+          <t>499ms</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>462ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>372ms</t>
+          <t>714ms</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>511ms</t>
+          <t>198ms</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>662ms</t>
+          <t>153ms</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>759ms</t>
+          <t>706ms</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>722ms</t>
+          <t>300ms</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>734ms</t>
+          <t>512ms</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>781ms</t>
+          <t>841ms</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>504ms</t>
+          <t>775ms</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>525ms</t>
+          <t>845ms</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>721ms</t>
+          <t>314ms</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>140ms</t>
+          <t>726ms</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>671ms</t>
+          <t>385ms</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>507ms</t>
+          <t>564ms</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>457ms</t>
+          <t>445ms</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>824ms</t>
+          <t>665ms</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>430ms</t>
+          <t>378ms</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>753ms</t>
+          <t>349ms</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>722ms</t>
+          <t>484ms</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>722ms</t>
+          <t>643ms</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>782ms</t>
+          <t>439ms</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>749ms</t>
+          <t>687ms</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>791ms</t>
+          <t>708ms</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>647ms</t>
+          <t>605ms</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>363ms</t>
+          <t>280ms</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>641ms</t>
+          <t>625ms</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>177ms</t>
+          <t>808ms</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>488ms</t>
+          <t>150ms</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>189ms</t>
+          <t>343ms</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>841ms</t>
+          <t>571ms</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>826ms</t>
+          <t>144ms</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>405ms</t>
+          <t>490ms</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>423ms</t>
+          <t>712ms</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>220ms</t>
+          <t>515ms</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>669ms</t>
+          <t>648ms</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>363ms</t>
+          <t>164ms</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>756ms</t>
+          <t>801ms</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>362ms</t>
+          <t>219ms</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>592ms</t>
+          <t>323ms</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>310ms</t>
+          <t>782ms</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>805ms</t>
+          <t>455ms</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>670ms</t>
+          <t>413ms</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>734ms</t>
+          <t>820ms</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>242ms</t>
+          <t>558ms</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>258ms</t>
+          <t>812ms</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>691ms</t>
+          <t>504ms</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>479ms</t>
+          <t>128ms</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>497ms</t>
+          <t>840ms</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>402ms</t>
+          <t>567ms</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>485ms</t>
+          <t>797ms</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>468ms</t>
+          <t>809ms</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>684ms</t>
+          <t>141ms</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>615ms</t>
+          <t>283ms</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>720ms</t>
+          <t>776ms</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>691ms</t>
+          <t>233ms</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>724ms</t>
+          <t>707ms</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>635ms</t>
+          <t>133ms</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>842ms</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>501ms</t>
+          <t>181ms</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>176ms</t>
+          <t>630ms</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>820ms</t>
+          <t>218ms</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>794ms</t>
+          <t>525ms</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>135ms</t>
+          <t>286ms</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>204ms</t>
+          <t>276ms</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>785ms</t>
+          <t>804ms</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>469ms</t>
+          <t>693ms</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>791ms</t>
+          <t>623ms</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>662ms</t>
+          <t>527ms</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>457ms</t>
+          <t>257ms</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>231ms</t>
+          <t>747ms</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>206ms</t>
+          <t>621ms</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>302ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>123ms</t>
+          <t>151ms</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>608ms</t>
+          <t>176ms</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>833ms</t>
+          <t>377ms</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -16059,7 +16059,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>290ms</t>
+          <t>823ms</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>696ms</t>
+          <t>674ms</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>569ms</t>
+          <t>588ms</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>758ms</t>
+          <t>666ms</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>733ms</t>
+          <t>395ms</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>387ms</t>
+          <t>359ms</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16437,7 +16437,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>373ms</t>
+          <t>541ms</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>215ms</t>
+          <t>763ms</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>594ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>286ms</t>
+          <t>680ms</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>121ms</t>
+          <t>292ms</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>534ms</t>
+          <t>292ms</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>434ms</t>
+          <t>429ms</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>807ms</t>
+          <t>142ms</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -16941,7 +16941,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>130ms</t>
+          <t>648ms</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>429ms</t>
+          <t>616ms</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>384ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>634ms</t>
+          <t>628ms</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -17193,7 +17193,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>289ms</t>
+          <t>320ms</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>631ms</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>402ms</t>
+          <t>406ms</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>394ms</t>
+          <t>639ms</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>830ms</t>
+          <t>241ms</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>775ms</t>
+          <t>719ms</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17571,7 +17571,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>419ms</t>
+          <t>294ms</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>692ms</t>
+          <t>302ms</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>163ms</t>
+          <t>504ms</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>337ms</t>
+          <t>587ms</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>593ms</t>
+          <t>251ms</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>633ms</t>
+          <t>575ms</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>453ms</t>
+          <t>268ms</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -18012,7 +18012,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>402ms</t>
+          <t>155ms</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>379ms</t>
+          <t>701ms</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>603ms</t>
+          <t>253ms</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>412ms</t>
+          <t>381ms</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>754ms</t>
+          <t>382ms</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>530ms</t>
+          <t>184ms</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>572ms</t>
+          <t>447ms</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>409ms</t>
+          <t>828ms</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>587ms</t>
+          <t>570ms</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>722ms</t>
+          <t>333ms</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>359ms</t>
+          <t>572ms</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -18705,7 +18705,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>308ms</t>
+          <t>462ms</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -18768,7 +18768,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>558ms</t>
+          <t>475ms</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>462ms</t>
+          <t>253ms</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>299ms</t>
+          <t>256ms</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>452ms</t>
+          <t>692ms</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>742ms</t>
+          <t>224ms</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>753ms</t>
+          <t>584ms</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>345ms</t>
+          <t>618ms</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>259ms</t>
+          <t>122ms</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>194ms</t>
+          <t>638ms</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>708ms</t>
+          <t>709ms</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>427ms</t>
+          <t>798ms</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
